--- a/StructureDefinition-emcare-encounter.xlsx
+++ b/StructureDefinition-emcare-encounter.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3143" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3142" uniqueCount="544">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-01-10T12:56:19+00:00</t>
+    <t>2022-01-18T13:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1030,7 +1030,7 @@
     <t>Encounter.participant.type</t>
   </si>
   <si>
-    <t>Role of participant in encounter</t>
+    <t>Participant type Person accompanying child</t>
   </si>
   <si>
     <t>Role of participant in encounter.</t>
@@ -1039,7 +1039,10 @@
     <t>The participant type indicates how an individual participates in an encounter. It includes non-practitioner participants, and for practitioners this is to describe the action type in the context of this encounter (e.g. Admitting Dr, Attending Dr, Translator, Consulting Dr). This is different to the practitioner roles which are functional roles, derived from terms of employment, education, licensing, etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://fhir.org/guides/who/emc-cds/ValueSet/emcare-a-de45</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE45</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1073,10 +1076,13 @@
 </t>
   </si>
   <si>
-    <t>Persons involved in the encounter other than the patient</t>
+    <t>Person accompanying child today</t>
   </si>
   <si>
     <t>Persons involved in the encounter other than the patient.</t>
+  </si>
+  <si>
+    <t>EmCare.A.DE44</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -7065,7 +7071,7 @@
         <v>76</v>
       </c>
       <c r="F45" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>86</v>
@@ -7112,11 +7118,9 @@
         <v>78</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="X45" s="2"/>
       <c r="Y45" t="s" s="2">
         <v>330</v>
       </c>
@@ -7151,24 +7155,24 @@
         <v>97</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>78</v>
+        <v>331</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -7194,10 +7198,10 @@
         <v>209</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -7248,7 +7252,7 @@
         <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>76</v>
@@ -7269,18 +7273,18 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7303,13 +7307,13 @@
         <v>86</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7360,7 +7364,7 @@
         <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>76</v>
@@ -7375,24 +7379,24 @@
         <v>97</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7415,13 +7419,13 @@
         <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
@@ -7472,7 +7476,7 @@
         <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>76</v>
@@ -7493,18 +7497,18 @@
         <v>315</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7530,13 +7534,13 @@
         <v>209</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
@@ -7586,7 +7590,7 @@
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>76</v>
@@ -7604,21 +7608,21 @@
         <v>78</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7730,7 +7734,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
@@ -7844,7 +7848,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7867,16 +7871,16 @@
         <v>86</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
@@ -7926,7 +7930,7 @@
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>76</v>
@@ -7935,30 +7939,30 @@
         <v>85</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>97</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -7981,23 +7985,23 @@
         <v>86</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="P53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q53" t="s" s="2">
         <v>78</v>
@@ -8042,7 +8046,7 @@
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>76</v>
@@ -8051,7 +8055,7 @@
         <v>85</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>97</v>
@@ -8063,18 +8067,18 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
@@ -8097,16 +8101,16 @@
         <v>78</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -8156,7 +8160,7 @@
         <v>78</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>76</v>
@@ -8174,25 +8178,25 @@
         <v>78</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -8214,13 +8218,13 @@
         <v>181</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
@@ -8250,7 +8254,7 @@
       </c>
       <c r="X55" s="2"/>
       <c r="Y55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Z55" t="s" s="2">
         <v>78</v>
@@ -8268,7 +8272,7 @@
         <v>78</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>76</v>
@@ -8283,28 +8287,28 @@
         <v>97</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" t="s" s="2">
@@ -8323,16 +8327,16 @@
         <v>86</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8382,7 +8386,7 @@
         <v>78</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>76</v>
@@ -8400,21 +8404,21 @@
         <v>78</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8440,10 +8444,10 @@
         <v>234</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8494,7 +8498,7 @@
         <v>78</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>76</v>
@@ -8515,7 +8519,7 @@
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>78</v>
@@ -8526,7 +8530,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8638,7 +8642,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8752,7 +8756,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8868,11 +8872,11 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" t="s" s="2">
@@ -8891,16 +8895,16 @@
         <v>86</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
@@ -8950,7 +8954,7 @@
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>85</v>
@@ -8968,21 +8972,21 @@
         <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
@@ -9008,10 +9012,10 @@
         <v>181</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
@@ -9041,10 +9045,10 @@
         <v>109</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Z62" t="s" s="2">
         <v>78</v>
@@ -9062,7 +9066,7 @@
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AF62" t="s" s="2">
         <v>76</v>
@@ -9094,7 +9098,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
@@ -9117,13 +9121,13 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
@@ -9174,7 +9178,7 @@
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AF63" t="s" s="2">
         <v>76</v>
@@ -9195,7 +9199,7 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>78</v>
@@ -9206,7 +9210,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
@@ -9229,16 +9233,16 @@
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
@@ -9288,7 +9292,7 @@
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>76</v>
@@ -9309,7 +9313,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9320,7 +9324,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
@@ -9346,13 +9350,13 @@
         <v>234</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
@@ -9402,7 +9406,7 @@
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AF65" t="s" s="2">
         <v>76</v>
@@ -9423,7 +9427,7 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9434,7 +9438,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
@@ -9546,7 +9550,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
@@ -9660,7 +9664,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B68" s="2"/>
       <c r="C68" t="s" s="2">
@@ -9776,7 +9780,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B69" s="2"/>
       <c r="C69" t="s" s="2">
@@ -9802,10 +9806,10 @@
         <v>153</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
@@ -9856,7 +9860,7 @@
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>76</v>
@@ -9883,12 +9887,12 @@
         <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B70" s="2"/>
       <c r="C70" t="s" s="2">
@@ -9911,13 +9915,13 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -9968,7 +9972,7 @@
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>76</v>
@@ -9989,7 +9993,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10000,7 +10004,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" t="s" s="2">
@@ -10026,10 +10030,10 @@
         <v>181</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
@@ -10059,10 +10063,10 @@
         <v>109</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Z71" t="s" s="2">
         <v>78</v>
@@ -10080,7 +10084,7 @@
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AF71" t="s" s="2">
         <v>76</v>
@@ -10101,18 +10105,18 @@
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B72" s="2"/>
       <c r="C72" t="s" s="2">
@@ -10138,10 +10142,10 @@
         <v>181</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
@@ -10171,10 +10175,10 @@
         <v>282</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Z72" t="s" s="2">
         <v>78</v>
@@ -10192,7 +10196,7 @@
         <v>78</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>76</v>
@@ -10219,12 +10223,12 @@
         <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B73" s="2"/>
       <c r="C73" t="s" s="2">
@@ -10250,16 +10254,16 @@
         <v>181</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>78</v>
@@ -10287,10 +10291,10 @@
         <v>282</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="Z73" t="s" s="2">
         <v>78</v>
@@ -10308,7 +10312,7 @@
         <v>78</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AF73" t="s" s="2">
         <v>76</v>
@@ -10329,18 +10333,18 @@
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B74" s="2"/>
       <c r="C74" t="s" s="2">
@@ -10366,10 +10370,10 @@
         <v>181</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
@@ -10399,10 +10403,10 @@
         <v>109</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="Z74" t="s" s="2">
         <v>78</v>
@@ -10420,7 +10424,7 @@
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>76</v>
@@ -10441,18 +10445,18 @@
         <v>78</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" t="s" s="2">
@@ -10478,10 +10482,10 @@
         <v>181</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
@@ -10511,10 +10515,10 @@
         <v>109</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="Z75" t="s" s="2">
         <v>78</v>
@@ -10532,7 +10536,7 @@
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AF75" t="s" s="2">
         <v>76</v>
@@ -10553,18 +10557,18 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" t="s" s="2">
@@ -10587,13 +10591,13 @@
         <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="M76" s="2"/>
       <c r="N76" s="2"/>
@@ -10644,7 +10648,7 @@
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AF76" t="s" s="2">
         <v>76</v>
@@ -10665,18 +10669,18 @@
         <v>78</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" t="s" s="2">
@@ -10702,10 +10706,10 @@
         <v>181</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -10735,10 +10739,10 @@
         <v>282</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>78</v>
@@ -10756,7 +10760,7 @@
         <v>78</v>
       </c>
       <c r="AE77" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AF77" t="s" s="2">
         <v>76</v>
@@ -10777,18 +10781,18 @@
         <v>78</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" t="s" s="2">
@@ -10814,13 +10818,13 @@
         <v>234</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
@@ -10870,7 +10874,7 @@
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AF78" t="s" s="2">
         <v>76</v>
@@ -10891,7 +10895,7 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
@@ -10902,7 +10906,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" t="s" s="2">
@@ -11014,7 +11018,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" t="s" s="2">
@@ -11128,7 +11132,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" t="s" s="2">
@@ -11244,7 +11248,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" t="s" s="2">
@@ -11267,13 +11271,13 @@
         <v>78</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
@@ -11324,7 +11328,7 @@
         <v>78</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AF82" t="s" s="2">
         <v>85</v>
@@ -11342,21 +11346,21 @@
         <v>78</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" t="s" s="2">
@@ -11382,13 +11386,13 @@
         <v>105</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
@@ -11417,10 +11421,10 @@
         <v>175</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Z83" t="s" s="2">
         <v>78</v>
@@ -11438,7 +11442,7 @@
         <v>78</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>76</v>
@@ -11459,7 +11463,7 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
@@ -11470,7 +11474,7 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" t="s" s="2">
@@ -11496,13 +11500,13 @@
         <v>181</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
@@ -11531,10 +11535,10 @@
         <v>282</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Z84" t="s" s="2">
         <v>78</v>
@@ -11552,7 +11556,7 @@
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>76</v>
@@ -11584,7 +11588,7 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" t="s" s="2">
@@ -11610,10 +11614,10 @@
         <v>209</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
@@ -11664,7 +11668,7 @@
         <v>78</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AF85" t="s" s="2">
         <v>76</v>
@@ -11685,7 +11689,7 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
@@ -11696,7 +11700,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" t="s" s="2">
@@ -11719,13 +11723,13 @@
         <v>78</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
@@ -11776,7 +11780,7 @@
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>76</v>
@@ -11794,21 +11798,21 @@
         <v>78</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" t="s" s="2">
@@ -11831,16 +11835,16 @@
         <v>78</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
@@ -11890,7 +11894,7 @@
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>76</v>
@@ -11908,10 +11912,10 @@
         <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
